--- a/DateBase/orders/Dang Nguyen48_2026-8-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-18.xlsx
@@ -1111,6 +1111,9 @@
       <c r="G2" t="str">
         <v>0571101161151041581055101030661010105510551010103030105101020307101010101051020556.510512101283.510105555101010310556</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
